--- a/output/pdf_financials_xlsx/WDGY.xlsx
+++ b/output/pdf_financials_xlsx/WDGY.xlsx
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>-0.011403</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.011148</v>
       </c>
     </row>
     <row r="92">
@@ -2676,7 +2676,11 @@
           <t>Foreign currency translation reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>-0.011403</v>
       </c>

--- a/output/pdf_financials_xlsx/WDGY.xlsx
+++ b/output/pdf_financials_xlsx/WDGY.xlsx
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.006037</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.550382</v>
+        <v>-1.556419</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-11.651343</v>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.550382</v>
+        <v>-1.556419</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-11.651343</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-180.7277453648927</v>
+        <v>-181.4314773475704</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-958.3532864438663</v>
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.09947599999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.118622</v>
       </c>
     </row>
     <row r="35">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.09947599999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.118622</v>
       </c>
     </row>
     <row r="37">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.110329</v>
+        <v>0.010853</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.14259</v>
+        <v>0.023968</v>
       </c>
     </row>
     <row r="49">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">

--- a/output/pdf_financials_xlsx/WDGY.xlsx
+++ b/output/pdf_financials_xlsx/WDGY.xlsx
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.279242</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.522355</v>
       </c>
     </row>
     <row r="68">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.05728</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.490702</v>
       </c>
     </row>
     <row r="111">
@@ -2816,7 +2816,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.05728</v>
       </c>
